--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536115_LIGAREGULARA_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536115_LIGAREGULARA_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,31 +558,31 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0872</v>
+        <v>4.3098</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3458</v>
+        <v>4.5683</v>
       </c>
       <c r="F2" t="n">
         <v>-0.2585</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0431</v>
+        <v>1.2657</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4168</v>
+        <v>2.0319</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.3738</v>
+        <v>-0.7662</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5306</v>
+        <v>2.7532</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9681</v>
+        <v>2.5832</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4375</v>
+        <v>0.17</v>
       </c>
       <c r="M2" t="n">
         <v>-1.4875</v>
@@ -629,7 +629,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. GARCIA MUÑOZ</t>
+          <t>A. GARRIDO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -641,67 +641,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2226</v>
+        <v>1.0116</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2226</v>
+        <v>1.4412</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0.4296</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2226</v>
+        <v>0.8185</v>
       </c>
       <c r="H3" t="n">
-        <v>0.615</v>
+        <v>0.7568</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6075</v>
+        <v>0.0617</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2226</v>
+        <v>2.6372</v>
       </c>
       <c r="K3" t="n">
-        <v>0.615</v>
+        <v>0.6931</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6075</v>
+        <v>1.9441</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-1.8186</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-1.8824</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1699</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.3649</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0.3864</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0.0261</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0.3603</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.3844</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.3844</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. GARRIDO RODRIGUEZ</t>
+          <t>A. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -724,67 +724,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0116</v>
+        <v>0.6089</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4412</v>
+        <v>0.6874</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4296</v>
+        <v>-0.0785</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8185</v>
+        <v>-2.0536</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7568</v>
+        <v>-2.8053</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0617</v>
+        <v>0.7516</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6372</v>
+        <v>0.3246</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6931</v>
+        <v>-0.955</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9441</v>
+        <v>1.2796</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.8186</v>
+        <v>-2.3782</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06370000000000001</v>
+        <v>-1.8503</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.8824</v>
+        <v>-0.5279</v>
       </c>
       <c r="P4" t="n">
-        <v>0.195</v>
+        <v>0.9749</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.1699</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3649</v>
+        <v>2.1448</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3864</v>
+        <v>-0.0895</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0261</v>
+        <v>-0.2445</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3603</v>
+        <v>0.1549</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3844</v>
+        <v>1.7772</v>
       </c>
       <c r="W4" t="n">
+        <v>1.7772</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.3844</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. HARGUINDEY MANEIRO</t>
+          <t>E. A NONGO BERTHOLD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -807,67 +807,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6089</v>
+        <v>0.3713</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6874</v>
+        <v>0.261</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0785</v>
+        <v>0.1103</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.0536</v>
+        <v>-0.3414</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.8053</v>
+        <v>0.1008</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7516</v>
+        <v>-0.4422</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3246</v>
+        <v>0.1915</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.955</v>
+        <v>-0.578</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2796</v>
+        <v>0.7695</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3782</v>
+        <v>-0.533</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8503</v>
+        <v>0.6788</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5279</v>
+        <v>-1.2118</v>
       </c>
       <c r="P5" t="n">
         <v>0.9749</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1699</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1448</v>
+        <v>0.9749</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0895</v>
+        <v>0.9049</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2445</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1549</v>
+        <v>0.8355</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7772</v>
+        <v>-1.1671</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7772</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.1671</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. A NONGO BERTHOLD</t>
+          <t>M. SERRANO ALVAREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,67 +890,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3713</v>
+        <v>0.3413</v>
       </c>
       <c r="E6" t="n">
-        <v>0.261</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1103</v>
+        <v>0.2693</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3414</v>
+        <v>-0.4643</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1008</v>
+        <v>-0.623</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4422</v>
+        <v>0.1587</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1915</v>
+        <v>1.1577</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.578</v>
+        <v>-0.7539</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7695</v>
+        <v>1.9116</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.533</v>
+        <v>-1.6219</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6788</v>
+        <v>0.1309</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2118</v>
+        <v>-1.7529</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9749</v>
+        <v>0.39</v>
       </c>
       <c r="Q6" t="n">
+        <v>-1.1699</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.5599</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.3844</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.3844</v>
+      </c>
+      <c r="X6" t="n">
         <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.9749</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.9049</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.06950000000000001</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.8355</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-1.1671</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-1.1671</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SERRANO ALVAREZ</t>
+          <t>D. ABREU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -973,64 +973,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3413</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.4555</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2693</v>
+        <v>-0.5357</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4643</v>
+        <v>-0.5988</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.623</v>
+        <v>-2.6173</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1587</v>
+        <v>2.0185</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1577</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7539</v>
+        <v>-1.656</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9116</v>
+        <v>2.4136</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6219</v>
+        <v>-1.3565</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1309</v>
+        <v>-0.9613</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7529</v>
+        <v>-0.3951</v>
       </c>
       <c r="P7" t="n">
-        <v>0.39</v>
+        <v>1.1699</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1699</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5599</v>
+        <v>1.1699</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8</v>
+        <v>-0.6513</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4686</v>
+        <v>-0.3021</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3313</v>
+        <v>-0.3492</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3844</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3844</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1044,7 +1044,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. ABREU</t>
+          <t>F. SIERRA GALA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1056,67 +1056,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.4647</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4555</v>
+        <v>0.5496</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5357</v>
+        <v>-1.0143</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5988</v>
+        <v>-2.3753</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.6173</v>
+        <v>-1.262</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0185</v>
+        <v>-1.1133</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7576000000000001</v>
+        <v>-0.8139</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.656</v>
+        <v>-0.6435</v>
       </c>
       <c r="L8" t="n">
-        <v>2.4136</v>
+        <v>-0.1705</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3565</v>
+        <v>-1.5613</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9613</v>
+        <v>-0.6185</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3951</v>
+        <v>-0.9428</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1699</v>
+        <v>1.7549</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1699</v>
+        <v>1.7549</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6513</v>
+        <v>0.4872</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3021</v>
+        <v>0.1964</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3492</v>
+        <v>0.2908</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.3315</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1671</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.4986</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. SIERRA GALA</t>
+          <t>N. PENA BANOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,64 +1139,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4647</v>
+        <v>-2.1503</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5496</v>
+        <v>-0.8118</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0143</v>
+        <v>-1.3384</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3753</v>
+        <v>-0.7573</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.262</v>
+        <v>-0.9339</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1133</v>
+        <v>0.1766</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8139</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6435</v>
+        <v>-0.66</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1705</v>
+        <v>0.0405</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5613</v>
+        <v>-0.1378</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6185</v>
+        <v>-0.2739</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9428</v>
+        <v>0.1361</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7549</v>
+        <v>0.39</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7549</v>
+        <v>0.39</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4872</v>
+        <v>-0.2843</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1964</v>
+        <v>-0.1923</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2908</v>
+        <v>-0.0919</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3315</v>
+        <v>-1.4986</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1671</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>-1.4986</v>
@@ -1210,7 +1210,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. PENA BANOS</t>
+          <t>R. HAYES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1222,58 +1222,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1503</v>
+        <v>-4.6092</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8118</v>
+        <v>-2.2672</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3384</v>
+        <v>-2.342</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7573</v>
+        <v>-3.3193</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9339</v>
+        <v>-2.2762</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1766</v>
+        <v>-1.0432</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.8789</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.66</v>
+        <v>-1.0409</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0405</v>
+        <v>0.162</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1378</v>
+        <v>-2.4404</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2739</v>
+        <v>-1.2353</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1361</v>
+        <v>-1.2052</v>
       </c>
       <c r="P10" t="n">
-        <v>0.39</v>
+        <v>0.585</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1699</v>
       </c>
       <c r="R10" t="n">
-        <v>0.39</v>
+        <v>1.7549</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2843</v>
+        <v>-0.3762</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1923</v>
+        <v>-0.2184</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0919</v>
+        <v>-0.1578</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4986</v>
@@ -1293,7 +1293,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. HAYES</t>
+          <t>H. SALOMON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,67 +1305,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6092</v>
+        <v>-7.456</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2672</v>
+        <v>-5.1336</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.342</v>
+        <v>-2.3224</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.3193</v>
+        <v>-4.3148</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.2762</v>
+        <v>-0.5091</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0432</v>
+        <v>-3.8057</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8789</v>
+        <v>-3.244</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0409</v>
+        <v>-1.324</v>
       </c>
       <c r="L11" t="n">
-        <v>0.162</v>
+        <v>-1.92</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.4404</v>
+        <v>-1.0708</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2353</v>
+        <v>0.8149</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2052</v>
+        <v>-1.8857</v>
       </c>
       <c r="P11" t="n">
-        <v>0.585</v>
+        <v>-0.9749</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1699</v>
+        <v>-1.9499</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7549</v>
+        <v>0.9749</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3762</v>
+        <v>0.2739</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2184</v>
+        <v>0.0603</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1578</v>
+        <v>0.2136</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4986</v>
+        <v>-2.4401</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4986</v>
+        <v>-2.4401</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>H. SALOMON</t>
+          <t>G. BLAT BAEZA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1388,67 +1388,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.456</v>
+        <v>-7.748</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.1336</v>
+        <v>-7.123</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3224</v>
+        <v>-0.6249</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.3148</v>
+        <v>-5.2088</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5091</v>
+        <v>-1.7432</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.8057</v>
+        <v>-3.4657</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.244</v>
+        <v>-4.059</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.324</v>
+        <v>-1.3934</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.92</v>
+        <v>-2.6655</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0708</v>
+        <v>-1.1499</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8149</v>
+        <v>-0.3497</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.8857</v>
+        <v>-0.8001</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9749</v>
+        <v>0.195</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.9499</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9749</v>
+        <v>2.1448</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2739</v>
+        <v>-0.2411</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0603</v>
+        <v>-0.4513</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2136</v>
+        <v>0.2102</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.4401</v>
+        <v>-2.493</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.6629</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.4401</v>
+        <v>-1.8301</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. BLAT BAEZA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1471,157 +1471,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.748</v>
+        <v>-15.8655</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.123</v>
+        <v>-7.3006</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6249</v>
+        <v>-8.5647</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.2088</v>
+        <v>-17.3494</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.7432</v>
+        <v>-9.8805</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.4657</v>
+        <v>-7.4692</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.059</v>
+        <v>-1.793500000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.3934</v>
+        <v>-5.7284</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.6655</v>
+        <v>3.9349</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1499</v>
+        <v>-15.5559</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3497</v>
+        <v>-4.152000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8001</v>
+        <v>-11.4041</v>
       </c>
       <c r="P13" t="n">
-        <v>0.195</v>
+        <v>6.8246</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9499</v>
+        <v>-8.7744</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1448</v>
+        <v>15.5988</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2411</v>
+        <v>0.2556999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4513</v>
+        <v>-0.6855</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2102</v>
+        <v>0.9412</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.493</v>
+        <v>-5.596</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.6629</v>
+        <v>3.9527</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.8301</v>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>play_by_play_2536115_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
+        <v>-9.5487</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. BURGOS CABALLERO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.8655</v>
+        <v>7.3597</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.300499999999999</v>
+        <v>6.0014</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.5647</v>
+        <v>1.3583</v>
       </c>
       <c r="G14" t="n">
-        <v>-17.3494</v>
+        <v>5.2222</v>
       </c>
       <c r="H14" t="n">
-        <v>-9.880599999999999</v>
+        <v>1.9237</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.4693</v>
+        <v>3.2985</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.793500000000001</v>
+        <v>5.4143</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.728499999999999</v>
+        <v>1.5912</v>
       </c>
       <c r="L14" t="n">
-        <v>3.9349</v>
+        <v>3.8232</v>
       </c>
       <c r="M14" t="n">
-        <v>-15.5559</v>
+        <v>-0.1921</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.152000000000001</v>
+        <v>0.3325</v>
       </c>
       <c r="O14" t="n">
-        <v>-11.4041</v>
+        <v>-0.5246</v>
       </c>
       <c r="P14" t="n">
-        <v>6.8246</v>
+        <v>0.39</v>
       </c>
       <c r="Q14" t="n">
-        <v>-8.7744</v>
+        <v>-1.1699</v>
       </c>
       <c r="R14" t="n">
-        <v>15.5988</v>
+        <v>1.5599</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2557000000000001</v>
+        <v>0.196</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6855</v>
+        <v>-0.0731</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9412</v>
+        <v>0.2691</v>
       </c>
       <c r="V14" t="n">
-        <v>-5.596</v>
+        <v>1.5515</v>
       </c>
       <c r="W14" t="n">
-        <v>3.9527</v>
+        <v>1.8301</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.5487</v>
-      </c>
-      <c r="Y14" t="inlineStr"/>
+        <v>-0.2786</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2536115_LIGAREGULARA_PROCESSED.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. BURGOS CABALLERO</t>
+          <t>T. SAGNA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1633,67 +1633,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.3597</v>
+        <v>6.9025</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0014</v>
+        <v>5.9039</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3583</v>
+        <v>0.9986</v>
       </c>
       <c r="G15" t="n">
-        <v>5.2222</v>
+        <v>3.8506</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9237</v>
+        <v>4.0319</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2985</v>
+        <v>-0.1813</v>
       </c>
       <c r="J15" t="n">
-        <v>5.4143</v>
+        <v>3.2997</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5912</v>
+        <v>3.2187</v>
       </c>
       <c r="L15" t="n">
-        <v>3.8232</v>
+        <v>0.081</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1921</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3325</v>
+        <v>0.8132</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5246</v>
+        <v>-0.2623</v>
       </c>
       <c r="P15" t="n">
-        <v>0.39</v>
+        <v>-0.7799</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1699</v>
+        <v>-0.9749</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5599</v>
+        <v>0.195</v>
       </c>
       <c r="S15" t="n">
-        <v>0.196</v>
+        <v>0.7288</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0731</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2691</v>
+        <v>0.8099</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5515</v>
+        <v>3.1031</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8301</v>
+        <v>3.6602</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2786</v>
+        <v>-0.5571</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. SAGNA</t>
+          <t>A. LAFUENTE SISO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,67 +1716,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.9025</v>
+        <v>5.0467</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9039</v>
+        <v>2.4324</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9986</v>
+        <v>2.6143</v>
       </c>
       <c r="G16" t="n">
-        <v>3.8506</v>
+        <v>2.9765</v>
       </c>
       <c r="H16" t="n">
-        <v>4.0319</v>
+        <v>-1.3684</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1813</v>
+        <v>4.345</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2997</v>
+        <v>1.7387</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2187</v>
+        <v>-2.5865</v>
       </c>
       <c r="L16" t="n">
-        <v>0.081</v>
+        <v>4.3252</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5508999999999999</v>
+        <v>1.2378</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8132</v>
+        <v>1.218</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2623</v>
+        <v>0.0198</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7799</v>
+        <v>-1.5599</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9749</v>
+        <v>-2.9248</v>
       </c>
       <c r="R16" t="n">
-        <v>0.195</v>
+        <v>1.3649</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7288</v>
+        <v>-0.0302</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.0418</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8099</v>
+        <v>0.0116</v>
       </c>
       <c r="V16" t="n">
-        <v>3.1031</v>
+        <v>3.6602</v>
       </c>
       <c r="W16" t="n">
         <v>3.6602</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5571</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. LAFUENTE SISO</t>
+          <t>K. NEWTON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,64 +1799,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.0467</v>
+        <v>4.9272</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4324</v>
+        <v>3.093</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6143</v>
+        <v>1.8342</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9765</v>
+        <v>2.4887</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3684</v>
+        <v>1.7078</v>
       </c>
       <c r="I17" t="n">
-        <v>4.345</v>
+        <v>0.7808</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7387</v>
+        <v>2.6857</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.5865</v>
+        <v>1.3736</v>
       </c>
       <c r="L17" t="n">
-        <v>4.3252</v>
+        <v>1.3121</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2378</v>
+        <v>-0.197</v>
       </c>
       <c r="N17" t="n">
-        <v>1.218</v>
+        <v>0.3342</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0198</v>
+        <v>-0.5312</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5599</v>
+        <v>0.9749</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9248</v>
+        <v>-0.195</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3649</v>
+        <v>1.1699</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0302</v>
+        <v>0.8535</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0418</v>
+        <v>-0.0077</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0116</v>
+        <v>0.8613</v>
       </c>
       <c r="V17" t="n">
-        <v>3.6602</v>
+        <v>0.61</v>
       </c>
       <c r="W17" t="n">
-        <v>3.6602</v>
+        <v>0.61</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. NEWTON</t>
+          <t>J. NVE MALEVA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.9272</v>
+        <v>2.3265</v>
       </c>
       <c r="E18" t="n">
-        <v>3.093</v>
+        <v>0.7267</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8342</v>
+        <v>1.5998</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4887</v>
+        <v>1.6867</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7078</v>
+        <v>1.9311</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7808</v>
+        <v>-0.2444</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6857</v>
+        <v>1.6082</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3736</v>
+        <v>1.3247</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3121</v>
+        <v>0.2835</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.197</v>
+        <v>0.0785</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3342</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5312</v>
+        <v>-0.5279</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9749</v>
+        <v>0.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.195</v>
+        <v>-1.1699</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1699</v>
+        <v>1.5599</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8535</v>
+        <v>1.8543</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0077</v>
+        <v>0.6728</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8613</v>
+        <v>1.1815</v>
       </c>
       <c r="V18" t="n">
-        <v>0.61</v>
+        <v>-1.6045</v>
       </c>
       <c r="W18" t="n">
-        <v>0.61</v>
+        <v>-0.3844</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. NVE MALEVA</t>
+          <t>P. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.3265</v>
+        <v>0.33</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7267</v>
+        <v>0.3005</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5998</v>
+        <v>0.0295</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6867</v>
+        <v>1.8408</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9311</v>
+        <v>2.1549</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2444</v>
+        <v>-0.3141</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6082</v>
+        <v>1.7621</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3247</v>
+        <v>1.6811</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2835</v>
+        <v>0.081</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0785</v>
+        <v>0.0786</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.4738</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5279</v>
+        <v>-0.3951</v>
       </c>
       <c r="P19" t="n">
-        <v>0.39</v>
+        <v>-0.39</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1699</v>
+        <v>-0.9749</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5599</v>
+        <v>0.585</v>
       </c>
       <c r="S19" t="n">
-        <v>1.8543</v>
+        <v>-0.5637</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6728</v>
+        <v>-0.4867</v>
       </c>
       <c r="U19" t="n">
-        <v>1.1815</v>
+        <v>-0.077</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.6045</v>
+        <v>-0.5571</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3844</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2201</v>
+        <v>-0.5571</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. CAMPENY LLOVERAS</t>
+          <t>J. SANTOS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.33</v>
+        <v>-0.3593</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3005</v>
+        <v>-0.159</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0295</v>
+        <v>-0.2003</v>
       </c>
       <c r="G20" t="n">
-        <v>1.8408</v>
+        <v>-0.3014</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1549</v>
+        <v>0.6156</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3141</v>
+        <v>-0.9169</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7621</v>
+        <v>-0.375</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6811</v>
+        <v>0.1435</v>
       </c>
       <c r="L20" t="n">
-        <v>0.081</v>
+        <v>-0.5185</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0786</v>
+        <v>0.0736</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4738</v>
+        <v>0.4721</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3951</v>
+        <v>-0.3984</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.39</v>
+        <v>0.585</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9749</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0.585</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5637</v>
+        <v>0.2457</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4867</v>
+        <v>0.216</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.077</v>
+        <v>0.0297</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5571</v>
+        <v>-0.8885999999999999</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5571</v>
+        <v>-0.8885999999999999</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. SANTOS RODRIGUEZ</t>
+          <t>H. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3593</v>
+        <v>-0.663</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.159</v>
+        <v>-1.6936</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2003</v>
+        <v>1.0306</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3014</v>
+        <v>-0.3703</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6156</v>
+        <v>0.5353</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9169</v>
+        <v>-0.9056</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.375</v>
+        <v>-0.5785</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1435</v>
+        <v>0.0615</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5185</v>
+        <v>-0.64</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0736</v>
+        <v>0.2082</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4721</v>
+        <v>0.4738</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3984</v>
+        <v>-0.2656</v>
       </c>
       <c r="P21" t="n">
-        <v>0.585</v>
+        <v>-0.7799</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1699</v>
       </c>
       <c r="R21" t="n">
-        <v>0.585</v>
+        <v>0.39</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2457</v>
+        <v>-0.1757</v>
       </c>
       <c r="T21" t="n">
-        <v>0.216</v>
+        <v>-0.2237</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0297</v>
+        <v>0.048</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8885999999999999</v>
+        <v>0.6629</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2786</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8885999999999999</v>
+        <v>0.3844</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. VAZQUEZ GARCIA</t>
+          <t>E. KALINICENKO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.663</v>
+        <v>-1.6582</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6936</v>
+        <v>-2.2286</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0306</v>
+        <v>0.5704</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3703</v>
+        <v>-0.2728</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5353</v>
+        <v>-1.8491</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9056</v>
+        <v>1.5763</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5785</v>
+        <v>-0.1415</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0615</v>
+        <v>-1.98</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.64</v>
+        <v>1.8386</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2082</v>
+        <v>-0.1314</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4738</v>
+        <v>0.1309</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2656</v>
+        <v>-0.2623</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7799</v>
+        <v>-1.5599</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1699</v>
+        <v>-2.1448</v>
       </c>
       <c r="R22" t="n">
-        <v>0.39</v>
+        <v>0.585</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1757</v>
+        <v>0.4001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2237</v>
+        <v>0.0577</v>
       </c>
       <c r="U22" t="n">
-        <v>0.048</v>
+        <v>0.3424</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6629</v>
+        <v>-0.2256</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2786</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3844</v>
+        <v>-0.2256</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. KALINICENKO</t>
+          <t>J. POTIER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6582</v>
+        <v>-1.8766</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2286</v>
+        <v>-1.7649</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5704</v>
+        <v>-0.1116</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2728</v>
+        <v>0.478</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.8491</v>
+        <v>0.9169</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5763</v>
+        <v>-0.4389</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1415</v>
+        <v>0.6717</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.98</v>
+        <v>0.5826</v>
       </c>
       <c r="L23" t="n">
-        <v>1.8386</v>
+        <v>0.089</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1314</v>
+        <v>-0.1937</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1309</v>
+        <v>0.3342</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2623</v>
+        <v>-0.5279</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5599</v>
+        <v>-1.3649</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1448</v>
+        <v>-1.9499</v>
       </c>
       <c r="R23" t="n">
         <v>0.585</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4001</v>
+        <v>-0.3796</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0577</v>
+        <v>-0.4867</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3424</v>
+        <v>0.1072</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2256</v>
+        <v>-0.61</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2256</v>
+        <v>-0.61</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. POTIER</t>
+          <t>V. ORLOV STURMAN MAURIN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,67 +2380,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8766</v>
+        <v>-3.4534</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7649</v>
+        <v>-4.0469</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1116</v>
+        <v>0.5935</v>
       </c>
       <c r="G24" t="n">
-        <v>0.478</v>
+        <v>-0.2493</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9169</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4389</v>
+        <v>0.47</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6717</v>
+        <v>-0.5295</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5826</v>
+        <v>-1.2585</v>
       </c>
       <c r="L24" t="n">
-        <v>0.089</v>
+        <v>0.729</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1937</v>
+        <v>0.2802</v>
       </c>
       <c r="N24" t="n">
-        <v>0.3342</v>
+        <v>0.5393</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5279</v>
+        <v>-0.259</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.3649</v>
+        <v>-2.7298</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9499</v>
+        <v>-2.9248</v>
       </c>
       <c r="R24" t="n">
-        <v>0.585</v>
+        <v>0.195</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3796</v>
+        <v>-0.3685</v>
       </c>
       <c r="T24" t="n">
         <v>-0.4867</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1072</v>
+        <v>0.1183</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.61</v>
+        <v>-0.1058</v>
       </c>
       <c r="W24" t="n">
+        <v>-0.1058</v>
+      </c>
+      <c r="X24" t="n">
         <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>-0.61</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>V. ORLOV STURMAN MAURIN</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2463,152 +2463,69 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.4534</v>
+        <v>18.8821</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.0469</v>
+        <v>8.564900000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5935</v>
+        <v>10.3173</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2493</v>
+        <v>17.3497</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7193000000000001</v>
+        <v>9.8804</v>
       </c>
       <c r="I25" t="n">
-        <v>0.47</v>
+        <v>7.469399999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.5295</v>
+        <v>15.5559</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.2585</v>
+        <v>4.1519</v>
       </c>
       <c r="L25" t="n">
-        <v>0.729</v>
+        <v>11.4041</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2802</v>
+        <v>1.7936</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5393</v>
+        <v>5.7284</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.259</v>
+        <v>-3.934499999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.7298</v>
+        <v>-6.8244</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.9248</v>
+        <v>-15.5988</v>
       </c>
       <c r="R25" t="n">
-        <v>0.195</v>
+        <v>8.7746</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3685</v>
+        <v>2.7607</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4867</v>
+        <v>-0.9410000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1183</v>
+        <v>3.702</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1058</v>
+        <v>5.596100000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.1058</v>
+        <v>9.5489</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>play_by_play_2536115_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>18.8821</v>
-      </c>
-      <c r="E26" t="n">
-        <v>8.564900000000002</v>
-      </c>
-      <c r="F26" t="n">
-        <v>10.3173</v>
-      </c>
-      <c r="G26" t="n">
-        <v>17.3497</v>
-      </c>
-      <c r="H26" t="n">
-        <v>9.8804</v>
-      </c>
-      <c r="I26" t="n">
-        <v>7.469399999999999</v>
-      </c>
-      <c r="J26" t="n">
-        <v>15.5559</v>
-      </c>
-      <c r="K26" t="n">
-        <v>4.1519</v>
-      </c>
-      <c r="L26" t="n">
-        <v>11.4041</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.7936</v>
-      </c>
-      <c r="N26" t="n">
-        <v>5.7284</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-3.934499999999999</v>
-      </c>
-      <c r="P26" t="n">
-        <v>-6.8244</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>-15.5988</v>
-      </c>
-      <c r="R26" t="n">
-        <v>8.7746</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.7607</v>
-      </c>
-      <c r="T26" t="n">
-        <v>-0.9410000000000001</v>
-      </c>
-      <c r="U26" t="n">
-        <v>3.702</v>
-      </c>
-      <c r="V26" t="n">
-        <v>5.596100000000001</v>
-      </c>
-      <c r="W26" t="n">
-        <v>9.5489</v>
-      </c>
-      <c r="X26" t="n">
         <v>-3.9527</v>
       </c>
-      <c r="Y26" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
